--- a/docs/データベース.xlsx
+++ b/docs/データベース.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yana/Downloads/VoiceTree/HP作成/260221_PICKUPLIVER/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162EDEA8-23FE-A54E-A793-04766E70D5BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DADC6D9A-DE1F-E840-8369-08A2815D453F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="960" yWindow="820" windowWidth="28300" windowHeight="17360" xr2:uid="{2141F815-2034-6D42-8FA2-D8076E8BD180}"/>
   </bookViews>
